--- a/metadata/Data 2024 For Syl Segmentation_2.xlsx
+++ b/metadata/Data 2024 For Syl Segmentation_2.xlsx
@@ -29491,7 +29491,7 @@
       <c r="D855" t="inlineStr"/>
       <c r="E855" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F855" t="n">
@@ -29525,7 +29525,7 @@
       <c r="D856" t="inlineStr"/>
       <c r="E856" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F856" t="n">
@@ -29559,7 +29559,7 @@
       <c r="D857" t="inlineStr"/>
       <c r="E857" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F857" t="n">
@@ -29593,7 +29593,7 @@
       <c r="D858" t="inlineStr"/>
       <c r="E858" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F858" t="n">
@@ -29627,7 +29627,7 @@
       <c r="D859" t="inlineStr"/>
       <c r="E859" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F859" t="n">
@@ -29661,7 +29661,7 @@
       <c r="D860" t="inlineStr"/>
       <c r="E860" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F860" t="n">
@@ -29695,7 +29695,7 @@
       <c r="D861" t="inlineStr"/>
       <c r="E861" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F861" t="n">
@@ -29729,7 +29729,7 @@
       <c r="D862" t="inlineStr"/>
       <c r="E862" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F862" t="n">
@@ -29763,7 +29763,7 @@
       <c r="D863" t="inlineStr"/>
       <c r="E863" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F863" t="n">
@@ -29797,7 +29797,7 @@
       <c r="D864" t="inlineStr"/>
       <c r="E864" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F864" t="n">
@@ -29831,7 +29831,7 @@
       <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F865" t="n">
@@ -29865,7 +29865,7 @@
       <c r="D866" t="inlineStr"/>
       <c r="E866" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F866" t="n">
@@ -29899,7 +29899,7 @@
       <c r="D867" t="inlineStr"/>
       <c r="E867" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F867" t="n">
@@ -29933,7 +29933,7 @@
       <c r="D868" t="inlineStr"/>
       <c r="E868" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F868" t="n">
@@ -29967,7 +29967,7 @@
       <c r="D869" t="inlineStr"/>
       <c r="E869" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F869" t="n">
@@ -30001,7 +30001,7 @@
       <c r="D870" t="inlineStr"/>
       <c r="E870" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F870" t="n">
@@ -30035,7 +30035,7 @@
       <c r="D871" t="inlineStr"/>
       <c r="E871" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F871" t="n">
@@ -30069,7 +30069,7 @@
       <c r="D872" t="inlineStr"/>
       <c r="E872" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F872" t="n">
@@ -30103,7 +30103,7 @@
       <c r="D873" t="inlineStr"/>
       <c r="E873" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F873" t="n">
@@ -30137,7 +30137,7 @@
       <c r="D874" t="inlineStr"/>
       <c r="E874" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F874" t="n">
@@ -30171,7 +30171,7 @@
       <c r="D875" t="inlineStr"/>
       <c r="E875" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F875" t="n">
@@ -30205,7 +30205,7 @@
       <c r="D876" t="inlineStr"/>
       <c r="E876" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F876" t="n">
@@ -30239,7 +30239,7 @@
       <c r="D877" t="inlineStr"/>
       <c r="E877" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F877" t="n">
@@ -30273,7 +30273,7 @@
       <c r="D878" t="inlineStr"/>
       <c r="E878" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F878" t="n">
@@ -30307,7 +30307,7 @@
       <c r="D879" t="inlineStr"/>
       <c r="E879" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F879" t="n">
@@ -30341,7 +30341,7 @@
       <c r="D880" t="inlineStr"/>
       <c r="E880" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F880" t="n">
@@ -30375,7 +30375,7 @@
       <c r="D881" t="inlineStr"/>
       <c r="E881" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F881" t="n">
@@ -30409,7 +30409,7 @@
       <c r="D882" t="inlineStr"/>
       <c r="E882" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F882" t="n">
@@ -30443,7 +30443,7 @@
       <c r="D883" t="inlineStr"/>
       <c r="E883" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F883" t="n">
@@ -30477,7 +30477,7 @@
       <c r="D884" t="inlineStr"/>
       <c r="E884" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F884" t="n">
@@ -30511,7 +30511,7 @@
       <c r="D885" t="inlineStr"/>
       <c r="E885" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F885" t="n">
@@ -30545,7 +30545,7 @@
       <c r="D886" t="inlineStr"/>
       <c r="E886" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F886" t="n">
@@ -30579,7 +30579,7 @@
       <c r="D887" t="inlineStr"/>
       <c r="E887" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F887" t="n">
@@ -30613,7 +30613,7 @@
       <c r="D888" t="inlineStr"/>
       <c r="E888" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F888" t="n">
@@ -30647,7 +30647,7 @@
       <c r="D889" t="inlineStr"/>
       <c r="E889" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F889" t="n">
@@ -30681,7 +30681,7 @@
       <c r="D890" t="inlineStr"/>
       <c r="E890" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F890" t="n">
@@ -30715,7 +30715,7 @@
       <c r="D891" t="inlineStr"/>
       <c r="E891" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F891" t="n">
@@ -30749,7 +30749,7 @@
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F892" t="n">
@@ -30783,7 +30783,7 @@
       <c r="D893" t="inlineStr"/>
       <c r="E893" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F893" t="n">
@@ -30817,7 +30817,7 @@
       <c r="D894" t="inlineStr"/>
       <c r="E894" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F894" t="n">
@@ -30851,7 +30851,7 @@
       <c r="D895" t="inlineStr"/>
       <c r="E895" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F895" t="n">
@@ -30885,7 +30885,7 @@
       <c r="D896" t="inlineStr"/>
       <c r="E896" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F896" t="n">
@@ -30919,7 +30919,7 @@
       <c r="D897" t="inlineStr"/>
       <c r="E897" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F897" t="n">
@@ -30953,7 +30953,7 @@
       <c r="D898" t="inlineStr"/>
       <c r="E898" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F898" t="n">
@@ -30987,7 +30987,7 @@
       <c r="D899" t="inlineStr"/>
       <c r="E899" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F899" t="n">
@@ -31021,7 +31021,7 @@
       <c r="D900" t="inlineStr"/>
       <c r="E900" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F900" t="n">
@@ -31055,7 +31055,7 @@
       <c r="D901" t="inlineStr"/>
       <c r="E901" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F901" t="n">
@@ -31089,7 +31089,7 @@
       <c r="D902" t="inlineStr"/>
       <c r="E902" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F902" t="n">
@@ -31123,7 +31123,7 @@
       <c r="D903" t="inlineStr"/>
       <c r="E903" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F903" t="n">
@@ -31157,7 +31157,7 @@
       <c r="D904" t="inlineStr"/>
       <c r="E904" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F904" t="n">
@@ -31191,7 +31191,7 @@
       <c r="D905" t="inlineStr"/>
       <c r="E905" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F905" t="n">
@@ -31225,7 +31225,7 @@
       <c r="D906" t="inlineStr"/>
       <c r="E906" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F906" t="n">
@@ -31259,7 +31259,7 @@
       <c r="D907" t="inlineStr"/>
       <c r="E907" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F907" t="n">
@@ -31293,7 +31293,7 @@
       <c r="D908" t="inlineStr"/>
       <c r="E908" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F908" t="n">
@@ -31327,7 +31327,7 @@
       <c r="D909" t="inlineStr"/>
       <c r="E909" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F909" t="n">
@@ -31361,7 +31361,7 @@
       <c r="D910" t="inlineStr"/>
       <c r="E910" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F910" t="n">
@@ -31395,7 +31395,7 @@
       <c r="D911" t="inlineStr"/>
       <c r="E911" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F911" t="n">
@@ -31429,7 +31429,7 @@
       <c r="D912" t="inlineStr"/>
       <c r="E912" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F912" t="n">
@@ -31463,7 +31463,7 @@
       <c r="D913" t="inlineStr"/>
       <c r="E913" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F913" t="n">
@@ -31497,7 +31497,7 @@
       <c r="D914" t="inlineStr"/>
       <c r="E914" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F914" t="n">
@@ -31531,7 +31531,7 @@
       <c r="D915" t="inlineStr"/>
       <c r="E915" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F915" t="n">
@@ -31565,7 +31565,7 @@
       <c r="D916" t="inlineStr"/>
       <c r="E916" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F916" t="n">
@@ -31599,7 +31599,7 @@
       <c r="D917" t="inlineStr"/>
       <c r="E917" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F917" t="n">
@@ -31633,7 +31633,7 @@
       <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F918" t="n">
@@ -31667,7 +31667,7 @@
       <c r="D919" t="inlineStr"/>
       <c r="E919" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F919" t="n">
@@ -31701,7 +31701,7 @@
       <c r="D920" t="inlineStr"/>
       <c r="E920" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F920" t="n">
@@ -31735,7 +31735,7 @@
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F921" t="n">
@@ -31769,7 +31769,7 @@
       <c r="D922" t="inlineStr"/>
       <c r="E922" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F922" t="n">
@@ -31803,7 +31803,7 @@
       <c r="D923" t="inlineStr"/>
       <c r="E923" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F923" t="n">
@@ -31837,7 +31837,7 @@
       <c r="D924" t="inlineStr"/>
       <c r="E924" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F924" t="n">
@@ -31871,7 +31871,7 @@
       <c r="D925" t="inlineStr"/>
       <c r="E925" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F925" t="n">
@@ -31905,7 +31905,7 @@
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F926" t="n">
@@ -31939,7 +31939,7 @@
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F927" t="n">
@@ -31973,7 +31973,7 @@
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F928" t="n">
@@ -32007,7 +32007,7 @@
       <c r="D929" t="inlineStr"/>
       <c r="E929" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F929" t="n">
@@ -32041,7 +32041,7 @@
       <c r="D930" t="inlineStr"/>
       <c r="E930" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F930" t="n">
@@ -32075,7 +32075,7 @@
       <c r="D931" t="inlineStr"/>
       <c r="E931" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F931" t="n">
@@ -32109,7 +32109,7 @@
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F932" t="n">
@@ -32143,7 +32143,7 @@
       <c r="D933" t="inlineStr"/>
       <c r="E933" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F933" t="n">
@@ -32177,7 +32177,7 @@
       <c r="D934" t="inlineStr"/>
       <c r="E934" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F934" t="n">
@@ -32211,7 +32211,7 @@
       <c r="D935" t="inlineStr"/>
       <c r="E935" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F935" t="n">
@@ -32245,7 +32245,7 @@
       <c r="D936" t="inlineStr"/>
       <c r="E936" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F936" t="n">
@@ -32279,7 +32279,7 @@
       <c r="D937" t="inlineStr"/>
       <c r="E937" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F937" t="n">
@@ -32313,7 +32313,7 @@
       <c r="D938" t="inlineStr"/>
       <c r="E938" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F938" t="n">
@@ -32347,7 +32347,7 @@
       <c r="D939" t="inlineStr"/>
       <c r="E939" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F939" t="n">
@@ -32381,7 +32381,7 @@
       <c r="D940" t="inlineStr"/>
       <c r="E940" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F940" t="n">
@@ -32415,7 +32415,7 @@
       <c r="D941" t="inlineStr"/>
       <c r="E941" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F941" t="n">
@@ -32449,7 +32449,7 @@
       <c r="D942" t="inlineStr"/>
       <c r="E942" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F942" t="n">
@@ -32483,7 +32483,7 @@
       <c r="D943" t="inlineStr"/>
       <c r="E943" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F943" t="n">
@@ -32517,7 +32517,7 @@
       <c r="D944" t="inlineStr"/>
       <c r="E944" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F944" t="n">
@@ -32551,7 +32551,7 @@
       <c r="D945" t="inlineStr"/>
       <c r="E945" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F945" t="n">
@@ -32585,7 +32585,7 @@
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F946" t="n">
@@ -32619,7 +32619,7 @@
       <c r="D947" t="inlineStr"/>
       <c r="E947" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F947" t="n">
@@ -32653,7 +32653,7 @@
       <c r="D948" t="inlineStr"/>
       <c r="E948" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F948" t="n">
@@ -32687,7 +32687,7 @@
       <c r="D949" t="inlineStr"/>
       <c r="E949" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F949" t="n">
@@ -32721,7 +32721,7 @@
       <c r="D950" t="inlineStr"/>
       <c r="E950" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F950" t="n">
@@ -32755,7 +32755,7 @@
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F951" t="n">
@@ -32789,7 +32789,7 @@
       <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F952" t="n">
@@ -32823,7 +32823,7 @@
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F953" t="n">
@@ -32857,7 +32857,7 @@
       <c r="D954" t="inlineStr"/>
       <c r="E954" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F954" t="n">
@@ -32891,7 +32891,7 @@
       <c r="D955" t="inlineStr"/>
       <c r="E955" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F955" t="n">
@@ -32925,7 +32925,7 @@
       <c r="D956" t="inlineStr"/>
       <c r="E956" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F956" t="n">
@@ -32959,7 +32959,7 @@
       <c r="D957" t="inlineStr"/>
       <c r="E957" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F957" t="n">
@@ -32993,7 +32993,7 @@
       <c r="D958" t="inlineStr"/>
       <c r="E958" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F958" t="n">
@@ -33027,7 +33027,7 @@
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F959" t="n">
@@ -33061,7 +33061,7 @@
       <c r="D960" t="inlineStr"/>
       <c r="E960" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F960" t="n">
@@ -33095,7 +33095,7 @@
       <c r="D961" t="inlineStr"/>
       <c r="E961" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F961" t="n">
@@ -33129,7 +33129,7 @@
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F962" t="n">
@@ -33163,7 +33163,7 @@
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F963" t="n">
@@ -33197,7 +33197,7 @@
       <c r="D964" t="inlineStr"/>
       <c r="E964" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F964" t="n">
@@ -33231,7 +33231,7 @@
       <c r="D965" t="inlineStr"/>
       <c r="E965" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F965" t="n">
@@ -33265,7 +33265,7 @@
       <c r="D966" t="inlineStr"/>
       <c r="E966" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F966" t="n">
@@ -33299,7 +33299,7 @@
       <c r="D967" t="inlineStr"/>
       <c r="E967" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F967" t="n">
@@ -33333,7 +33333,7 @@
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F968" t="n">
@@ -33367,7 +33367,7 @@
       <c r="D969" t="inlineStr"/>
       <c r="E969" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F969" t="n">
@@ -33401,7 +33401,7 @@
       <c r="D970" t="inlineStr"/>
       <c r="E970" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F970" t="n">
@@ -33435,7 +33435,7 @@
       <c r="D971" t="inlineStr"/>
       <c r="E971" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F971" t="n">
@@ -33469,7 +33469,7 @@
       <c r="D972" t="inlineStr"/>
       <c r="E972" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F972" t="n">
@@ -33503,7 +33503,7 @@
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F973" t="n">
@@ -33537,7 +33537,7 @@
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F974" t="n">
@@ -33571,7 +33571,7 @@
       <c r="D975" t="inlineStr"/>
       <c r="E975" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F975" t="n">
@@ -33605,7 +33605,7 @@
       <c r="D976" t="inlineStr"/>
       <c r="E976" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F976" t="n">
@@ -33639,7 +33639,7 @@
       <c r="D977" t="inlineStr"/>
       <c r="E977" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F977" t="n">
@@ -33673,7 +33673,7 @@
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F978" t="n">
@@ -33707,7 +33707,7 @@
       <c r="D979" t="inlineStr"/>
       <c r="E979" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F979" t="n">
@@ -33741,7 +33741,7 @@
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F980" t="n">
@@ -33775,7 +33775,7 @@
       <c r="D981" t="inlineStr"/>
       <c r="E981" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F981" t="n">
@@ -33809,7 +33809,7 @@
       <c r="D982" t="inlineStr"/>
       <c r="E982" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F982" t="n">
@@ -33843,7 +33843,7 @@
       <c r="D983" t="inlineStr"/>
       <c r="E983" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F983" t="n">
@@ -33877,7 +33877,7 @@
       <c r="D984" t="inlineStr"/>
       <c r="E984" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F984" t="n">
@@ -33911,7 +33911,7 @@
       <c r="D985" t="inlineStr"/>
       <c r="E985" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F985" t="n">
@@ -33945,7 +33945,7 @@
       <c r="D986" t="inlineStr"/>
       <c r="E986" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F986" t="n">
@@ -33979,7 +33979,7 @@
       <c r="D987" t="inlineStr"/>
       <c r="E987" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F987" t="n">
@@ -34013,7 +34013,7 @@
       <c r="D988" t="inlineStr"/>
       <c r="E988" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F988" t="n">
@@ -34047,7 +34047,7 @@
       <c r="D989" t="inlineStr"/>
       <c r="E989" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F989" t="n">
@@ -34081,7 +34081,7 @@
       <c r="D990" t="inlineStr"/>
       <c r="E990" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F990" t="n">
@@ -34115,7 +34115,7 @@
       <c r="D991" t="inlineStr"/>
       <c r="E991" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F991" t="n">
@@ -34149,7 +34149,7 @@
       <c r="D992" t="inlineStr"/>
       <c r="E992" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F992" t="n">
@@ -34183,7 +34183,7 @@
       <c r="D993" t="inlineStr"/>
       <c r="E993" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F993" t="n">
@@ -34217,7 +34217,7 @@
       <c r="D994" t="inlineStr"/>
       <c r="E994" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F994" t="n">
@@ -34251,7 +34251,7 @@
       <c r="D995" t="inlineStr"/>
       <c r="E995" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F995" t="n">
@@ -34285,7 +34285,7 @@
       <c r="D996" t="inlineStr"/>
       <c r="E996" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F996" t="n">
@@ -34319,7 +34319,7 @@
       <c r="D997" t="inlineStr"/>
       <c r="E997" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F997" t="n">
@@ -34353,7 +34353,7 @@
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F998" t="n">
@@ -34387,7 +34387,7 @@
       <c r="D999" t="inlineStr"/>
       <c r="E999" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F999" t="n">
@@ -34421,7 +34421,7 @@
       <c r="D1000" t="inlineStr"/>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1000" t="n">
@@ -34455,7 +34455,7 @@
       <c r="D1001" t="inlineStr"/>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1001" t="n">
@@ -34489,7 +34489,7 @@
       <c r="D1002" t="inlineStr"/>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1002" t="n">
@@ -34523,7 +34523,7 @@
       <c r="D1003" t="inlineStr"/>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1003" t="n">
@@ -34557,7 +34557,7 @@
       <c r="D1004" t="inlineStr"/>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1004" t="n">
@@ -34591,7 +34591,7 @@
       <c r="D1005" t="inlineStr"/>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1005" t="n">
@@ -34625,7 +34625,7 @@
       <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1006" t="n">
@@ -34659,7 +34659,7 @@
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1007" t="n">
@@ -34693,7 +34693,7 @@
       <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1008" t="n">
@@ -34727,7 +34727,7 @@
       <c r="D1009" t="inlineStr"/>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1009" t="n">
@@ -34761,7 +34761,7 @@
       <c r="D1010" t="inlineStr"/>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1010" t="n">
@@ -34795,7 +34795,7 @@
       <c r="D1011" t="inlineStr"/>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1011" t="n">
@@ -34829,7 +34829,7 @@
       <c r="D1012" t="inlineStr"/>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1012" t="n">
@@ -34863,7 +34863,7 @@
       <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1013" t="n">
@@ -34897,7 +34897,7 @@
       <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1014" t="n">
@@ -34931,7 +34931,7 @@
       <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1015" t="n">
@@ -34965,7 +34965,7 @@
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1016" t="n">
@@ -34999,7 +34999,7 @@
       <c r="D1017" t="inlineStr"/>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1017" t="n">
@@ -35033,7 +35033,7 @@
       <c r="D1018" t="inlineStr"/>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1018" t="n">
@@ -35067,7 +35067,7 @@
       <c r="D1019" t="inlineStr"/>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1019" t="n">
@@ -35101,7 +35101,7 @@
       <c r="D1020" t="inlineStr"/>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1020" t="n">
@@ -35135,7 +35135,7 @@
       <c r="D1021" t="inlineStr"/>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1021" t="n">
@@ -35169,7 +35169,7 @@
       <c r="D1022" t="inlineStr"/>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1022" t="n">
@@ -35203,7 +35203,7 @@
       <c r="D1023" t="inlineStr"/>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1023" t="n">
@@ -35237,7 +35237,7 @@
       <c r="D1024" t="inlineStr"/>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1024" t="n">
@@ -35271,7 +35271,7 @@
       <c r="D1025" t="inlineStr"/>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1025" t="n">
@@ -35305,7 +35305,7 @@
       <c r="D1026" t="inlineStr"/>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1026" t="n">
@@ -35339,7 +35339,7 @@
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1027" t="n">
@@ -35373,7 +35373,7 @@
       <c r="D1028" t="inlineStr"/>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1028" t="n">
@@ -35407,7 +35407,7 @@
       <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1029" t="n">
@@ -35441,7 +35441,7 @@
       <c r="D1030" t="inlineStr"/>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1030" t="n">
@@ -35475,7 +35475,7 @@
       <c r="D1031" t="inlineStr"/>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1031" t="n">
@@ -35509,7 +35509,7 @@
       <c r="D1032" t="inlineStr"/>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1032" t="n">
@@ -35543,7 +35543,7 @@
       <c r="D1033" t="inlineStr"/>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1033" t="n">
@@ -35577,7 +35577,7 @@
       <c r="D1034" t="inlineStr"/>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1034" t="n">
@@ -35611,7 +35611,7 @@
       <c r="D1035" t="inlineStr"/>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1035" t="n">
@@ -35645,7 +35645,7 @@
       <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1036" t="n">
@@ -35679,7 +35679,7 @@
       <c r="D1037" t="inlineStr"/>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1037" t="n">
@@ -35713,7 +35713,7 @@
       <c r="D1038" t="inlineStr"/>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1038" t="n">
@@ -35747,7 +35747,7 @@
       <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1039" t="n">
@@ -35781,7 +35781,7 @@
       <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1040" t="n">
@@ -35815,7 +35815,7 @@
       <c r="D1041" t="inlineStr"/>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1041" t="n">
@@ -35849,7 +35849,7 @@
       <c r="D1042" t="inlineStr"/>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1042" t="n">
@@ -35883,7 +35883,7 @@
       <c r="D1043" t="inlineStr"/>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1043" t="n">
@@ -35917,7 +35917,7 @@
       <c r="D1044" t="inlineStr"/>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1044" t="n">
@@ -35951,7 +35951,7 @@
       <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1045" t="n">
@@ -35985,7 +35985,7 @@
       <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1046" t="n">
@@ -36019,7 +36019,7 @@
       <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1047" t="n">
@@ -36053,7 +36053,7 @@
       <c r="D1048" t="inlineStr"/>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1048" t="n">
@@ -36087,7 +36087,7 @@
       <c r="D1049" t="inlineStr"/>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1049" t="n">
@@ -36121,7 +36121,7 @@
       <c r="D1050" t="inlineStr"/>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1050" t="n">
@@ -36155,7 +36155,7 @@
       <c r="D1051" t="inlineStr"/>
       <c r="E1051" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1051" t="n">
@@ -36189,7 +36189,7 @@
       <c r="D1052" t="inlineStr"/>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1052" t="n">
@@ -36223,7 +36223,7 @@
       <c r="D1053" t="inlineStr"/>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1053" t="n">
@@ -36257,7 +36257,7 @@
       <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1054" t="n">
@@ -36291,7 +36291,7 @@
       <c r="D1055" t="inlineStr"/>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1055" t="n">
@@ -36325,7 +36325,7 @@
       <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1056" t="n">
@@ -36359,7 +36359,7 @@
       <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1057" t="n">
@@ -36393,7 +36393,7 @@
       <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1058" t="n">
@@ -36427,7 +36427,7 @@
       <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1059" t="n">
@@ -36461,7 +36461,7 @@
       <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1060" t="n">
@@ -36495,7 +36495,7 @@
       <c r="D1061" t="inlineStr"/>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1061" t="n">
@@ -36529,7 +36529,7 @@
       <c r="D1062" t="inlineStr"/>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1062" t="n">
@@ -36563,7 +36563,7 @@
       <c r="D1063" t="inlineStr"/>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1063" t="n">
@@ -36597,7 +36597,7 @@
       <c r="D1064" t="inlineStr"/>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1064" t="n">
@@ -36631,7 +36631,7 @@
       <c r="D1065" t="inlineStr"/>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1065" t="n">
@@ -36665,7 +36665,7 @@
       <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1066" t="n">
@@ -36699,7 +36699,7 @@
       <c r="D1067" t="inlineStr"/>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1067" t="n">
@@ -36733,7 +36733,7 @@
       <c r="D1068" t="inlineStr"/>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1068" t="n">
@@ -36767,7 +36767,7 @@
       <c r="D1069" t="inlineStr"/>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1069" t="n">
@@ -36801,7 +36801,7 @@
       <c r="D1070" t="inlineStr"/>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1070" t="n">
@@ -36835,7 +36835,7 @@
       <c r="D1071" t="inlineStr"/>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1071" t="n">
@@ -36869,7 +36869,7 @@
       <c r="D1072" t="inlineStr"/>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1072" t="n">
@@ -36903,7 +36903,7 @@
       <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1073" t="n">
@@ -36937,7 +36937,7 @@
       <c r="D1074" t="inlineStr"/>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1074" t="n">
@@ -36971,7 +36971,7 @@
       <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1075" t="n">
@@ -37005,7 +37005,7 @@
       <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1076" t="n">
@@ -37039,7 +37039,7 @@
       <c r="D1077" t="inlineStr"/>
       <c r="E1077" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1077" t="n">
@@ -37073,7 +37073,7 @@
       <c r="D1078" t="inlineStr"/>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1078" t="n">
@@ -37107,7 +37107,7 @@
       <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1079" t="n">
@@ -37141,7 +37141,7 @@
       <c r="D1080" t="inlineStr"/>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1080" t="n">
@@ -37175,7 +37175,7 @@
       <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1081" t="n">
@@ -37209,7 +37209,7 @@
       <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1082" t="n">
@@ -37243,7 +37243,7 @@
       <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1083" t="n">
@@ -37277,7 +37277,7 @@
       <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1084" t="n">
@@ -37311,7 +37311,7 @@
       <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1085" t="n">
@@ -37345,7 +37345,7 @@
       <c r="D1086" t="inlineStr"/>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1086" t="n">
@@ -37379,7 +37379,7 @@
       <c r="D1087" t="inlineStr"/>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1087" t="n">
@@ -37413,7 +37413,7 @@
       <c r="D1088" t="inlineStr"/>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1088" t="n">
@@ -37447,7 +37447,7 @@
       <c r="D1089" t="inlineStr"/>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1089" t="n">
@@ -37481,7 +37481,7 @@
       <c r="D1090" t="inlineStr"/>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1090" t="n">
@@ -37515,7 +37515,7 @@
       <c r="D1091" t="inlineStr"/>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1091" t="n">
@@ -37549,7 +37549,7 @@
       <c r="D1092" t="inlineStr"/>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1092" t="n">
@@ -37583,7 +37583,7 @@
       <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1093" t="n">
@@ -37617,7 +37617,7 @@
       <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1094" t="n">
@@ -37651,7 +37651,7 @@
       <c r="D1095" t="inlineStr"/>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1095" t="n">
@@ -37685,7 +37685,7 @@
       <c r="D1096" t="inlineStr"/>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1096" t="n">
@@ -37719,7 +37719,7 @@
       <c r="D1097" t="inlineStr"/>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1097" t="n">
@@ -37753,7 +37753,7 @@
       <c r="D1098" t="inlineStr"/>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1098" t="n">
@@ -37787,7 +37787,7 @@
       <c r="D1099" t="inlineStr"/>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1099" t="n">
@@ -37821,7 +37821,7 @@
       <c r="D1100" t="inlineStr"/>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1100" t="n">
@@ -37855,7 +37855,7 @@
       <c r="D1101" t="inlineStr"/>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1101" t="n">
@@ -37889,7 +37889,7 @@
       <c r="D1102" t="inlineStr"/>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1102" t="n">
@@ -37923,7 +37923,7 @@
       <c r="D1103" t="inlineStr"/>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1103" t="n">
@@ -37957,7 +37957,7 @@
       <c r="D1104" t="inlineStr"/>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1104" t="n">
@@ -37991,7 +37991,7 @@
       <c r="D1105" t="inlineStr"/>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1105" t="n">
@@ -38025,7 +38025,7 @@
       <c r="D1106" t="inlineStr"/>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1106" t="n">
@@ -38059,7 +38059,7 @@
       <c r="D1107" t="inlineStr"/>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1107" t="n">
@@ -38093,7 +38093,7 @@
       <c r="D1108" t="inlineStr"/>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1108" t="n">
@@ -38127,7 +38127,7 @@
       <c r="D1109" t="inlineStr"/>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1109" t="n">
@@ -38161,7 +38161,7 @@
       <c r="D1110" t="inlineStr"/>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1110" t="n">
@@ -38195,7 +38195,7 @@
       <c r="D1111" t="inlineStr"/>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1111" t="n">
@@ -38229,7 +38229,7 @@
       <c r="D1112" t="inlineStr"/>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1112" t="n">
@@ -38263,7 +38263,7 @@
       <c r="D1113" t="inlineStr"/>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1113" t="n">
@@ -38297,7 +38297,7 @@
       <c r="D1114" t="inlineStr"/>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1114" t="n">
@@ -38331,7 +38331,7 @@
       <c r="D1115" t="inlineStr"/>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1115" t="n">
@@ -38365,7 +38365,7 @@
       <c r="D1116" t="inlineStr"/>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1116" t="n">
@@ -38399,7 +38399,7 @@
       <c r="D1117" t="inlineStr"/>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1117" t="n">
@@ -38433,7 +38433,7 @@
       <c r="D1118" t="inlineStr"/>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1118" t="n">
@@ -38467,7 +38467,7 @@
       <c r="D1119" t="inlineStr"/>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1119" t="n">
@@ -38501,7 +38501,7 @@
       <c r="D1120" t="inlineStr"/>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1120" t="n">
@@ -38535,7 +38535,7 @@
       <c r="D1121" t="inlineStr"/>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1121" t="n">
@@ -38569,7 +38569,7 @@
       <c r="D1122" t="inlineStr"/>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1122" t="n">
@@ -38603,7 +38603,7 @@
       <c r="D1123" t="inlineStr"/>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1123" t="n">
@@ -38637,7 +38637,7 @@
       <c r="D1124" t="inlineStr"/>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1124" t="n">
@@ -38671,7 +38671,7 @@
       <c r="D1125" t="inlineStr"/>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1125" t="n">
@@ -38705,7 +38705,7 @@
       <c r="D1126" t="inlineStr"/>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1126" t="n">
@@ -38739,7 +38739,7 @@
       <c r="D1127" t="inlineStr"/>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1127" t="n">
@@ -38773,7 +38773,7 @@
       <c r="D1128" t="inlineStr"/>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1128" t="n">
@@ -38807,7 +38807,7 @@
       <c r="D1129" t="inlineStr"/>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1129" t="n">
@@ -38841,7 +38841,7 @@
       <c r="D1130" t="inlineStr"/>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1130" t="n">
@@ -38875,7 +38875,7 @@
       <c r="D1131" t="inlineStr"/>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1131" t="n">
@@ -38909,7 +38909,7 @@
       <c r="D1132" t="inlineStr"/>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1132" t="n">
@@ -38943,7 +38943,7 @@
       <c r="D1133" t="inlineStr"/>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1133" t="n">
@@ -38977,7 +38977,7 @@
       <c r="D1134" t="inlineStr"/>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1134" t="n">
@@ -39011,7 +39011,7 @@
       <c r="D1135" t="inlineStr"/>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1135" t="n">
@@ -39045,7 +39045,7 @@
       <c r="D1136" t="inlineStr"/>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1136" t="n">
@@ -39079,7 +39079,7 @@
       <c r="D1137" t="inlineStr"/>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1137" t="n">
@@ -39113,7 +39113,7 @@
       <c r="D1138" t="inlineStr"/>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1138" t="n">
@@ -39147,7 +39147,7 @@
       <c r="D1139" t="inlineStr"/>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1139" t="n">
@@ -39181,7 +39181,7 @@
       <c r="D1140" t="inlineStr"/>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1140" t="n">
@@ -39215,7 +39215,7 @@
       <c r="D1141" t="inlineStr"/>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1141" t="n">
@@ -39249,7 +39249,7 @@
       <c r="D1142" t="inlineStr"/>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1142" t="n">
@@ -39283,7 +39283,7 @@
       <c r="D1143" t="inlineStr"/>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1143" t="n">
@@ -39317,7 +39317,7 @@
       <c r="D1144" t="inlineStr"/>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1144" t="n">
@@ -39351,7 +39351,7 @@
       <c r="D1145" t="inlineStr"/>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1145" t="n">
@@ -39385,7 +39385,7 @@
       <c r="D1146" t="inlineStr"/>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1146" t="n">
@@ -39419,7 +39419,7 @@
       <c r="D1147" t="inlineStr"/>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1147" t="n">
@@ -39453,7 +39453,7 @@
       <c r="D1148" t="inlineStr"/>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1148" t="n">
@@ -39487,7 +39487,7 @@
       <c r="D1149" t="inlineStr"/>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1149" t="n">
@@ -39521,7 +39521,7 @@
       <c r="D1150" t="inlineStr"/>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1150" t="n">
@@ -39555,7 +39555,7 @@
       <c r="D1151" t="inlineStr"/>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1151" t="n">
@@ -39589,7 +39589,7 @@
       <c r="D1152" t="inlineStr"/>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1152" t="n">
@@ -39623,7 +39623,7 @@
       <c r="D1153" t="inlineStr"/>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1153" t="n">
@@ -39657,7 +39657,7 @@
       <c r="D1154" t="inlineStr"/>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1154" t="n">
@@ -39691,7 +39691,7 @@
       <c r="D1155" t="inlineStr"/>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1155" t="n">
@@ -39725,7 +39725,7 @@
       <c r="D1156" t="inlineStr"/>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1156" t="n">
@@ -39759,7 +39759,7 @@
       <c r="D1157" t="inlineStr"/>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1157" t="n">
@@ -39793,7 +39793,7 @@
       <c r="D1158" t="inlineStr"/>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1158" t="n">
@@ -39827,7 +39827,7 @@
       <c r="D1159" t="inlineStr"/>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1159" t="n">
@@ -39861,7 +39861,7 @@
       <c r="D1160" t="inlineStr"/>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1160" t="n">
@@ -39895,7 +39895,7 @@
       <c r="D1161" t="inlineStr"/>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1161" t="n">
@@ -39929,7 +39929,7 @@
       <c r="D1162" t="inlineStr"/>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1162" t="n">
@@ -39963,7 +39963,7 @@
       <c r="D1163" t="inlineStr"/>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1163" t="n">
@@ -39997,7 +39997,7 @@
       <c r="D1164" t="inlineStr"/>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1164" t="n">
@@ -40031,7 +40031,7 @@
       <c r="D1165" t="inlineStr"/>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1165" t="n">
@@ -40065,7 +40065,7 @@
       <c r="D1166" t="inlineStr"/>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1166" t="n">
@@ -40099,7 +40099,7 @@
       <c r="D1167" t="inlineStr"/>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1167" t="n">
@@ -40133,7 +40133,7 @@
       <c r="D1168" t="inlineStr"/>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1168" t="n">
@@ -40167,7 +40167,7 @@
       <c r="D1169" t="inlineStr"/>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1169" t="n">
@@ -40201,7 +40201,7 @@
       <c r="D1170" t="inlineStr"/>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1170" t="n">
@@ -40235,7 +40235,7 @@
       <c r="D1171" t="inlineStr"/>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1171" t="n">
@@ -40269,7 +40269,7 @@
       <c r="D1172" t="inlineStr"/>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1172" t="n">
@@ -40303,7 +40303,7 @@
       <c r="D1173" t="inlineStr"/>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1173" t="n">
@@ -40337,7 +40337,7 @@
       <c r="D1174" t="inlineStr"/>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1174" t="n">
@@ -40371,7 +40371,7 @@
       <c r="D1175" t="inlineStr"/>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1175" t="n">
@@ -40405,7 +40405,7 @@
       <c r="D1176" t="inlineStr"/>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1176" t="n">
@@ -40439,7 +40439,7 @@
       <c r="D1177" t="inlineStr"/>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1177" t="n">
@@ -40473,7 +40473,7 @@
       <c r="D1178" t="inlineStr"/>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1178" t="n">
@@ -40507,7 +40507,7 @@
       <c r="D1179" t="inlineStr"/>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1179" t="n">
@@ -40541,7 +40541,7 @@
       <c r="D1180" t="inlineStr"/>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1180" t="n">
@@ -40575,7 +40575,7 @@
       <c r="D1181" t="inlineStr"/>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1181" t="n">
@@ -40609,7 +40609,7 @@
       <c r="D1182" t="inlineStr"/>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1182" t="n">
@@ -40643,7 +40643,7 @@
       <c r="D1183" t="inlineStr"/>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1183" t="n">
@@ -40677,7 +40677,7 @@
       <c r="D1184" t="inlineStr"/>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1184" t="n">
@@ -40711,7 +40711,7 @@
       <c r="D1185" t="inlineStr"/>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1185" t="n">
@@ -40745,7 +40745,7 @@
       <c r="D1186" t="inlineStr"/>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1186" t="n">
@@ -40779,7 +40779,7 @@
       <c r="D1187" t="inlineStr"/>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1187" t="n">
@@ -40813,7 +40813,7 @@
       <c r="D1188" t="inlineStr"/>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1188" t="n">
@@ -40847,7 +40847,7 @@
       <c r="D1189" t="inlineStr"/>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1189" t="n">
@@ -40881,7 +40881,7 @@
       <c r="D1190" t="inlineStr"/>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1190" t="n">
@@ -40915,7 +40915,7 @@
       <c r="D1191" t="inlineStr"/>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1191" t="n">
@@ -40949,7 +40949,7 @@
       <c r="D1192" t="inlineStr"/>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1192" t="n">
@@ -40983,7 +40983,7 @@
       <c r="D1193" t="inlineStr"/>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1193" t="n">
@@ -41017,7 +41017,7 @@
       <c r="D1194" t="inlineStr"/>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1194" t="n">
@@ -41051,7 +41051,7 @@
       <c r="D1195" t="inlineStr"/>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1195" t="n">
@@ -41085,7 +41085,7 @@
       <c r="D1196" t="inlineStr"/>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1196" t="n">
@@ -41119,7 +41119,7 @@
       <c r="D1197" t="inlineStr"/>
       <c r="E1197" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1197" t="n">
@@ -41153,7 +41153,7 @@
       <c r="D1198" t="inlineStr"/>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1198" t="n">
@@ -41187,7 +41187,7 @@
       <c r="D1199" t="inlineStr"/>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1199" t="n">
@@ -41221,7 +41221,7 @@
       <c r="D1200" t="inlineStr"/>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1200" t="n">
@@ -41255,7 +41255,7 @@
       <c r="D1201" t="inlineStr"/>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F1201" t="n">
